--- a/data/trans_orig/IP16B02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B02-Edad-trans_orig.xlsx
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>55538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78912</t>
+          <t>78049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44064</t>
+          <t>44273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41892</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>15441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>68961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121270</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>27491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25131</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>55696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49505</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>91907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103806</t>
+          <t>103862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
